--- a/artfynd/S 617-2023 artfynd.xlsx
+++ b/artfynd/S 617-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ35"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2098,10 +2098,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>63870364</v>
+        <v>136498571</v>
       </c>
       <c r="B14" t="n">
-        <v>57144</v>
+        <v>57193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,56 +2109,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>1K+</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>sävsjöström, Aborrgölsbrännan, Sm</t>
+          <t>Kärngöl, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>526840</v>
+        <v>527709</v>
       </c>
       <c r="R14" t="n">
-        <v>6315308</v>
+        <v>6316112</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2182,12 +2171,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-02-23</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-02-23</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Årskull. Flög upp från blåbärsriset.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,41 +2192,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Tallsumpskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>per taube</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>per taube</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63870364</t>
+          <t>https://artportalen.se/Sighting/136498571</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122341834</v>
+        <v>63870364</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>57144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,16 +2224,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2262,31 +2246,34 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1K+</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Höneström, F.d torpet Ryd, Höneskruv, Sm</t>
+          <t>sävsjöström, Aborrgölsbrännan, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530296</v>
+        <v>526840</v>
       </c>
       <c r="R15" t="n">
-        <v>6315435</v>
+        <v>6315308</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2310,22 +2297,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2017-02-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2017-02-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,31 +2313,41 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Tallsumpskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Katharina Ahlert</t>
+          <t>per taube</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Katharina Ahlert</t>
+          <t>per taube</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122341834</t>
+          <t>https://artportalen.se/Sighting/63870364</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122341830</v>
+        <v>122341834</v>
       </c>
       <c r="B16" t="n">
-        <v>57144</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,16 +2355,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2387,19 +2374,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -2416,13 +2395,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530395</v>
+        <v>530296</v>
       </c>
       <c r="R16" t="n">
-        <v>6315348</v>
+        <v>6315435</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2487,54 +2466,75 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122341830</t>
+          <t>https://artportalen.se/Sighting/122341834</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>80773650</v>
+        <v>122341830</v>
       </c>
       <c r="B17" t="n">
-        <v>75428</v>
+        <v>57144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>102613</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Utterhultsbäcken, Sm</t>
+          <t>Höneström, F.d torpet Ryd, Höneskruv, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529120</v>
+        <v>530395</v>
       </c>
       <c r="R17" t="n">
-        <v>6314881</v>
+        <v>6315348</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2561,17 +2561,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>riklig på senvuxna granar</t>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2580,63 +2585,60 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emil Persson</t>
+          <t>Katharina Ahlert</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emil Persson</t>
+          <t>Katharina Ahlert</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80773650</t>
+          <t>https://artportalen.se/Sighting/122341830</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>80773659</v>
+        <v>80773650</v>
       </c>
       <c r="B18" t="n">
-        <v>5179</v>
+        <v>75428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2682,6 +2684,11 @@
           <t>2019-11-05</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>riklig på senvuxna granar</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2706,16 +2713,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80773659</t>
+          <t>https://artportalen.se/Sighting/80773650</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>80773662</v>
+        <v>80773659</v>
       </c>
       <c r="B19" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2723,21 +2730,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2814,54 +2821,59 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80773662</t>
+          <t>https://artportalen.se/Sighting/80773659</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>62981829</v>
+        <v>80773662</v>
       </c>
       <c r="B20" t="n">
-        <v>92310</v>
+        <v>5199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>303</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenporing</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ceriporia excelsa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S. Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brotorpabäck, Sm</t>
+          <t>Utterhultsbäcken, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524988</v>
+        <v>529120</v>
       </c>
       <c r="R20" t="n">
-        <v>6315867</v>
+        <v>6314881</v>
       </c>
       <c r="S20" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2885,12 +2897,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>1995-10-12</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1995-10-12</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2899,33 +2911,34 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sonja Darell</t>
+          <t>Emil Persson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Annchristin Nyström</t>
+          <t>Emil Persson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62981829</t>
+          <t>https://artportalen.se/Sighting/80773662</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>62982102</v>
+        <v>62981829</v>
       </c>
       <c r="B21" t="n">
-        <v>88422</v>
+        <v>92310</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,21 +2946,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1007</v>
+        <v>303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stäppröksvamp</t>
+          <t>Rosenporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycoperdon decipiens</t>
+          <t>Ceriporia excelsa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Durieu &amp; Mont.</t>
+          <t>(S. Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3018,16 +3031,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62982102</t>
+          <t>https://artportalen.se/Sighting/62981829</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>62981859</v>
+        <v>62982102</v>
       </c>
       <c r="B22" t="n">
-        <v>92521</v>
+        <v>88422</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,21 +3048,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1177</v>
+        <v>1007</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brödmärgsticka</t>
+          <t>Stäppröksvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perenniporia medulla-panis</t>
+          <t>Lycoperdon decipiens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Jacq.) Donk</t>
+          <t>Durieu &amp; Mont.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3120,16 +3133,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62981859</t>
+          <t>https://artportalen.se/Sighting/62982102</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>62981883</v>
+        <v>62981859</v>
       </c>
       <c r="B23" t="n">
-        <v>93136</v>
+        <v>92521</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3137,21 +3150,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2075</v>
+        <v>1177</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Brödmärgsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Perenniporia medulla-panis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Jacq.) Donk</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3222,38 +3235,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62981883</t>
+          <t>https://artportalen.se/Sighting/62981859</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>62981945</v>
+        <v>62981883</v>
       </c>
       <c r="B24" t="n">
-        <v>89106</v>
+        <v>93136</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4394</v>
+        <v>2075</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3293,12 +3306,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>1993-09-02</t>
+          <t>1995-10-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1993-09-02</t>
+          <t>1995-10-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3324,16 +3337,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62981945</t>
+          <t>https://artportalen.se/Sighting/62981883</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>62981959</v>
+        <v>62981945</v>
       </c>
       <c r="B25" t="n">
-        <v>91087</v>
+        <v>89106</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3341,21 +3354,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4823</v>
+        <v>4394</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hasselsopp</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leccinellum pseudoscabrum</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kallenb.) Mikšík</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3395,12 +3408,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>1995-10-12</t>
+          <t>1993-09-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1995-10-12</t>
+          <t>1993-09-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3409,7 +3422,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3427,38 +3439,38 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62981959</t>
+          <t>https://artportalen.se/Sighting/62981945</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>62981864</v>
+        <v>62981959</v>
       </c>
       <c r="B26" t="n">
-        <v>91867</v>
+        <v>91087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5445</v>
+        <v>4823</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Hasselsopp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Leccinellum pseudoscabrum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kallenb.) Mikšík</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3512,6 +3524,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3529,38 +3542,38 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62981864</t>
+          <t>https://artportalen.se/Sighting/62981959</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>62981987</v>
+        <v>62981864</v>
       </c>
       <c r="B27" t="n">
-        <v>89894</v>
+        <v>91867</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5573</v>
+        <v>5445</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Småskölding</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pluteus nanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers. : Fr.) P. Kumm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3631,16 +3644,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62981987</t>
+          <t>https://artportalen.se/Sighting/62981864</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2453682</v>
+        <v>62981987</v>
       </c>
       <c r="B28" t="n">
-        <v>99022</v>
+        <v>89894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3648,51 +3661,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220093</v>
+        <v>5573</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Småskölding</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Pluteus nanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Pers. : Fr.) P. Kumm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Östraby, Sm</t>
+          <t>Brotorpabäck, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523817</v>
+        <v>524988</v>
       </c>
       <c r="R28" t="n">
-        <v>6314827</v>
+        <v>6315867</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3716,12 +3715,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2001-06-23</t>
+          <t>1995-10-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2001-06-23</t>
+          <t>1995-10-12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3732,36 +3731,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>gungfly</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jörg Adelmann</t>
+          <t>Sonja Darell</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jörg Adelmann</t>
+          <t>Annchristin Nyström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2453682</t>
+          <t>https://artportalen.se/Sighting/62981987</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>62981944</v>
+        <v>2453682</v>
       </c>
       <c r="B29" t="n">
-        <v>89079</v>
+        <v>99022</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,37 +3763,51 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>239209</v>
+        <v>220093</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kantarellvaxing</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brotorpabäck, Sm</t>
+          <t>Östraby, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524988</v>
+        <v>523817</v>
       </c>
       <c r="R29" t="n">
-        <v>6315867</v>
+        <v>6314827</v>
       </c>
       <c r="S29" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3823,12 +3831,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>1995-10-12</t>
+          <t>2001-06-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>1995-10-12</t>
+          <t>2001-06-23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3839,31 +3847,36 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>gungfly</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sonja Darell</t>
+          <t>Jörg Adelmann</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Annchristin Nyström</t>
+          <t>Jörg Adelmann</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62981944</t>
+          <t>https://artportalen.se/Sighting/2453682</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>63953610</v>
+        <v>62981944</v>
       </c>
       <c r="B30" t="n">
-        <v>57899</v>
+        <v>89079</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3871,52 +3884,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100067</v>
+        <v>239209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Kantarellvaxing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Hygrocybe cantharellus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Aborragölsbrännan, Sm</t>
+          <t>Brotorpabäck, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527175</v>
+        <v>524988</v>
       </c>
       <c r="R30" t="n">
-        <v>6314017</v>
+        <v>6315867</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3940,17 +3938,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2017-02-25</t>
+          <t>1995-10-12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2017-02-25</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Måttlig höjd mot väster</t>
+          <t>1995-10-12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3965,27 +3958,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Mikael Persson</t>
+          <t>Sonja Darell</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Mikael Persson</t>
+          <t>Annchristin Nyström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63953610</t>
+          <t>https://artportalen.se/Sighting/62981944</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133079382</v>
+        <v>63953610</v>
       </c>
       <c r="B31" t="n">
-        <v>56915</v>
+        <v>57899</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3993,16 +3986,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100088</v>
+        <v>100067</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4015,7 +4008,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>adult</t>
@@ -4024,10 +4016,9 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Aborragölsbrännan, Sm</t>
@@ -4064,12 +4055,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2017-02-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2017-02-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Måttlig höjd mot väster</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4078,7 +4074,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4090,22 +4085,22 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Mikael Persson, Therese Petersson</t>
+          <t>Mikael Persson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133079382</t>
+          <t>https://artportalen.se/Sighting/63953610</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133067534</v>
+        <v>133079382</v>
       </c>
       <c r="B32" t="n">
-        <v>57162</v>
+        <v>56915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4113,21 +4108,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>100088</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4135,12 +4130,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -4186,27 +4182,18 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4218,22 +4205,22 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mikael Persson, Therese Petersson, Ulrika Petersson</t>
+          <t>Mikael Persson, Therese Petersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133067534</t>
+          <t>https://artportalen.se/Sighting/133079382</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>62907507</v>
+        <v>133067534</v>
       </c>
       <c r="B33" t="n">
-        <v>57144</v>
+        <v>57162</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4241,21 +4228,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4266,14 +4253,15 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Aborragölsbrännan, Sm</t>
@@ -4310,17 +4298,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2017-01-21</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2017-01-21</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Bubblade på friskt öven efter lunchtid</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4340,44 +4333,44 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Mikael Persson, Therese Petersson</t>
+          <t>Mikael Persson, Therese Petersson, Ulrika Petersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62907507</t>
+          <t>https://artportalen.se/Sighting/133067534</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>69239608</v>
+        <v>62907507</v>
       </c>
       <c r="B34" t="n">
-        <v>56522</v>
+        <v>57144</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>206004</v>
+        <v>102613</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4386,13 +4379,16 @@
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Aborragölsbrännan, Sm</t>
@@ -4429,12 +4425,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2018-01-27</t>
+          <t>2017-01-21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2018-01-27</t>
+          <t>2017-01-21</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Bubblade på friskt öven efter lunchtid</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4454,22 +4455,22 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mikael Persson, Roger Jönsson</t>
+          <t>Mikael Persson, Therese Petersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69239608</t>
+          <t>https://artportalen.se/Sighting/62907507</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>25041</v>
+        <v>69239608</v>
       </c>
       <c r="B35" t="n">
-        <v>56689</v>
+        <v>56522</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4477,21 +4478,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>206046</v>
+        <v>206004</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4499,16 +4500,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Aborragölsbrännan, Sm</t>
@@ -4545,12 +4544,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2018-01-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2018-01-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4570,11 +4569,127 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Mikael Persson</t>
+          <t>Mikael Persson, Roger Jönsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69239608</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>25041</v>
+      </c>
+      <c r="B36" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Aborragölsbrännan, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>527175</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6314017</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lenhovda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2010-07-31</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2010-07-31</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mikael Persson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Mikael Persson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/25041</t>
         </is>
@@ -4616,6 +4731,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
